--- a/www/download/COUNTRY.KOR.WIOD13.xlsx
+++ b/www/download/COUNTRY.KOR.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>769.230769191585</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>806.451604195844</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>934.579434669612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1388.88887012112</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1190.47621025982</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>1136.36362231776</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1298.70133322324</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1250.00002742103</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1190.47619916019</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1149.42530127868</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1020.40814942861</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>952.380984338174</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>925.925956818682</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1081.23300950843</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1270.08966179751</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.398</t>
+          <t>0.10303149833752</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.837</t>
+          <t>0.150707634675457</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.201</t>
+          <t>0.280489126551564</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.918</t>
+          <t>0.44861126704603</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20.277</t>
+          <t>0.500555868766896</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.136</t>
+          <t>0.469169357801223</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.557</t>
+          <t>0.445997582831108</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.152</t>
+          <t>0.488319584750837</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>0.406989670051751</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22.534</t>
+          <t>0.423440555937979</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>0.388448552835148</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>23.133</t>
+          <t>0.349227234621504</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>23.418</t>
+          <t>0.383632007794584</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>23.561</t>
+          <t>0.509411760039127</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>0.587188976766977</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12.899</t>
+          <t>1.00379363292628</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>1.0463781165663</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.405</t>
+          <t>1.25571092560575</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.296</t>
+          <t>1.53777023104975</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12.663</t>
+          <t>1.5749187612181</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.361</t>
+          <t>1.49446196846496</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13.659</t>
+          <t>1.57347622778517</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.182</t>
+          <t>1.49779794709675</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.403</t>
+          <t>1.33515176442308</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14.894</t>
+          <t>1.33458365304332</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>1.34989658122701</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15.551</t>
+          <t>1.27855570295368</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>1.31885765384974</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>16.067</t>
+          <t>1.53603872456038</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.019</t>
+          <t>1.68788362417922</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>51162.193</t>
+          <t>1.24215878967394</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50854.307</t>
+          <t>1.33612731149781</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51302.684</t>
+          <t>1.58661916004688</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48438.841</t>
+          <t>1.92416787136737</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50338.267</t>
+          <t>1.86016470879422</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>51635.805</t>
+          <t>1.83392178615626</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>52111.252</t>
+          <t>2.04273334221779</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53200.369</t>
+          <t>2.0031498832562</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53124.252</t>
+          <t>1.82261284417025</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>55887.331</t>
+          <t>1.84476355518047</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>54220.887</t>
+          <t>1.7438493304473</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>54641.266</t>
+          <t>1.66638848917751</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>53454.996</t>
+          <t>1.72768383786683</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>53781.163</t>
+          <t>1.98089235479632</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>53619.22</t>
+          <t>2.17731596148098</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32640.761</t>
+          <t>82837912823.7267</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32366.566</t>
+          <t>83103349493.7171</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32542.482</t>
+          <t>81610557126.3679</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29972.52</t>
+          <t>69543847014.3562</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31616.61</t>
+          <t>77369935833.8894</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>32772.416</t>
+          <t>81236413772.1868</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33139.63</t>
+          <t>78941018954.4088</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34146.109</t>
+          <t>80418840494.682</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>34675.124</t>
+          <t>82947034026.9753</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>37056.547</t>
+          <t>89630697754.2896</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>36350.538</t>
+          <t>89709035227.4483</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>36940.81</t>
+          <t>94075168157.9105</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>36652.904</t>
+          <t>94219311804.9905</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36876.55</t>
+          <t>97020095947.4748</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>36765.509</t>
+          <t>88956901017.916</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>19867654482.6334</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>19354607615.1318</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>17751351782.5212</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>14788621583.1125</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>15408052573.9551</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>16358004816.2097</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>16610774947.207</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>17405937348.9905</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>18874667181.8763</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>20133000533.9385</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20261057197.436</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>21237881116.0136</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20637904071.2022</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>19015599201.1569</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17967497457.859</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>2834390.91948254</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>2644671.02365652</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>2777721.93042901</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>3273374.23602873</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2981393.20360304</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>2763364.68705036</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>2943038.18430007</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>2705740.23898546</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>2503124.63497982</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>2297935.57842268</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1911106.54918065</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1747138.24467854</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1556233.05213108</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1559943.85736557</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1650828.67454238</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>222807.599441667</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>218213.382737141</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>213427.441321738</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>195129.274730705</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>204732.738345309</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>218895.529216924</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>209682.066917968</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>214853.039849718</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>232565.224135765</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>265760.043239129</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>272933.312637219</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>285063.076008834</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>314597.533264145</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>350420.007798331</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>325882.621906374</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>644915.771121175</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>651792.438503643</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>635973.608593673</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>538967.475975637</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>612640.26830685</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32.71</t>
+          <t>669287.993048738</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>633334.354798539</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>659585.298803112</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>732811.780791009</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>872670.482822036</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>935443.708401949</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1028118.66801933</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1164892.09135486</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1328003.31037595</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1135792.79695094</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>0.642909617692244</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>0.672292562213195</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>0.833239632962865</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.59</t>
+          <t>1.0267284191536</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>1.05195368170717</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>1.00344825565788</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>0.995068290308986</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>0.961750654015098</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>0.837125074236327</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>0.840587397755457</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.794108647777444</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.739383039009935</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.775999338199113</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.939278877319591</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>1.04622313075151</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>145696.578353875</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>157916.283100464</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>149880.616669633</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>109034.361969183</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>149560.652840448</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>152282.883464335</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>136027.183614188</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>150481.669533285</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>166132.54815961</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>179596.344587704</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>207968.219166837</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>234877.971577669</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>254781.297508674</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>247386.29513268</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>222547.759311959</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>769.230769191585</t>
+          <t>1540.24765351061</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>806.451604195844</t>
+          <t>1466.2581526615</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>934.579434669612</t>
+          <t>1324.23362793892</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1388.88887012112</t>
+          <t>1202.71808580941</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1190.47621025982</t>
+          <t>1216.777428252</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1136.36362231776</t>
+          <t>1224.3099181356</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1298.70133322324</t>
+          <t>1216.10476222322</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1250.00002742103</t>
+          <t>1227.32600119803</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1190.47619916019</t>
+          <t>1310.46776240202</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1149.42530127868</t>
+          <t>1351.75241935937</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1020.40814942861</t>
+          <t>1334.19315141815</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>952.380984338174</t>
+          <t>1365.69231020601</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>925.925956818682</t>
+          <t>1292.29205204773</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1081.23300950843</t>
+          <t>1183.486220594</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1270.08966179751</t>
+          <t>1121.63223780674</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>10935421753.2105</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>11908111152.9406</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>12044511895.0338</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>9332847946.55429</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>11631459261.293</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>13157191747.3351</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>13571304581.1035</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>16313148127.8427</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>18556343450.1388</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>21292612986.8166</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>21550247922.1934</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>22826825913.3819</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>22973161122.0581</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>18040861091.4716</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>16375328069.2304</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>10602764446.9388</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>11845174759.7003</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>12101501403.2014</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>9059398286.52102</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>11693733716.0162</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>13814739760.2606</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>14224320143.0051</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>17024011120.139</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>19221328460.9459</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>21849421520.3816</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>22224774560.4139</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>23736855317.781</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>23851322816.9971</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>19348081808.9367</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>17211566878.6697</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>332657306.271696</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>62936393.2402781</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.816</t>
+          <t>-56989508.1676392</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>273449660.033268</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>-62274454.7232245</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>-657548012.925512</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>-653015561.901695</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>-710862992.296211</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>-664985010.807177</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>-556808533.565002</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>-674526638.220535</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.142</t>
+          <t>-910029404.399098</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.441</t>
+          <t>-878161694.939005</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.361</t>
+          <t>-1307220717.46509</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>-836238809.439315</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>2530.48768358049</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>2452.01260298029</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>2427.63757003982</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2437.58292473996</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>2496.77092371987</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>2452.84156987341</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>2426.2120488053</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>2407.70758553998</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>2407.49318528712</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2488.01846795831</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>2393.68747076475</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.185</t>
+          <t>2375.46204087862</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2295.10982919673</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>2295.10982919673</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.087</t>
+          <t>2295.10982919673</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>2508.19654903997</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>2440.5771832087</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>2419.82376783477</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>2431.91289060475</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>2482.530329715</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>2443.02633205807</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>2417.37033627695</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>2401.60567988671</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>2401.96463982723</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>2480.13361301885</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2374.98409023748</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>2362.04840706289</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>2282.64563697712</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>2282.64563697712</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>2282.64563697712</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>148197.732393644</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>154555.396206786</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>168054.217503683</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>154804.50024608</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>166448.652207662</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>199000.056707812</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>174125.463571877</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>186166.474305133</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>223611.742831462</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>289120.505801717</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>327909.56113519</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>373577.44620443</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>436153.453196744</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>494948.776622255</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>407710.185299997</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>100.35</t>
+          <t>13614167961.3728</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>104.61</t>
+          <t>13308803685.618</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>125.55</t>
+          <t>14882553500.3984</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>153.78</t>
+          <t>15596720990.1909</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>162.25</t>
+          <t>15332542007.0601</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>149.42</t>
+          <t>16095297171.3141</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>157.28</t>
+          <t>15351070448.7137</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>149.71</t>
+          <t>14730808155.0643</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>133.49</t>
+          <t>16231427759.2647</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>133.45</t>
+          <t>18949543732.8571</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>134.97</t>
+          <t>18098493659.4102</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>127.84</t>
+          <t>18974945267.2941</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>131.85</t>
+          <t>19865383778.273</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>153.63</t>
+          <t>22565176397.01</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>168.79</t>
+          <t>19956911877.8997</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>124.19</t>
+          <t>140581.430961096</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>133.59</t>
+          <t>157516.01026986</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>158.63</t>
+          <t>157672.57675118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>192.42</t>
+          <t>106221.758194344</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>191.3</t>
+          <t>130177.744039377</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>183.36</t>
+          <t>173153.47173526</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>204.19</t>
+          <t>153240.259906808</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>164700.969649037</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>182.23</t>
+          <t>193962.743807858</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>184.46</t>
+          <t>240516.625421563</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>174.36</t>
+          <t>281709.808589289</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>166.62</t>
+          <t>331011.002020373</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>172.73</t>
+          <t>385382.978704207</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>198.12</t>
+          <t>473784.922435432</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>217.73</t>
+          <t>352512.873467787</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51162.193</t>
+          <t>23373645755.4605</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50854.307</t>
+          <t>25655723783.1936</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>51302.684</t>
+          <t>25506423530.3031</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48438.841</t>
+          <t>17930862160.2321</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>50338.267</t>
+          <t>21509196809.6122</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>51635.805</t>
+          <t>25415614393.4226</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>52111.252</t>
+          <t>25662661166.408</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53200.369</t>
+          <t>27731271431.4636</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>53124.252</t>
+          <t>30470384264.4292</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>55887.331</t>
+          <t>33751576654.1443</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>54220.887</t>
+          <t>33930296477.0734</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>54641.266</t>
+          <t>36995819783.3333</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>53454.996</t>
+          <t>37785169873.4766</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>53781.163</t>
+          <t>38741445662.3559</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>53619.22</t>
+          <t>30984706658.8684</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>32640.761</t>
+          <t>7616.30143254875</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>32366.566</t>
+          <t>-2960.61406307348</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32542.482</t>
+          <t>10381.6407525029</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29972.52</t>
+          <t>48582.7420517361</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31616.61</t>
+          <t>36270.9081682852</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>32772.416</t>
+          <t>25846.5849725521</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>33139.63</t>
+          <t>20885.2036650692</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>34146.109</t>
+          <t>21465.5046560963</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>34675.124</t>
+          <t>29648.9990236033</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>37056.547</t>
+          <t>48603.8803801539</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>36350.538</t>
+          <t>46199.752545901</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>36940.81</t>
+          <t>42566.4441840567</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>36652.904</t>
+          <t>50770.4744925373</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>36876.55</t>
+          <t>21163.8541868228</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>36765.509</t>
+          <t>55197.31183221</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>82855.312</t>
+          <t>-9759477794.08767</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>83117.096</t>
+          <t>-12346920097.5756</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81621.534</t>
+          <t>-10623870029.9048</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69542.037</t>
+          <t>-2334141170.04112</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>75388.533</t>
+          <t>-6176654802.55203</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>81245.8</t>
+          <t>-9320317222.10852</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>78979.348</t>
+          <t>-10311590717.6943</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>80462.901</t>
+          <t>-13000463276.3994</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>82958.72</t>
+          <t>-14238956505.1645</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>89646.514</t>
+          <t>-14802032921.2872</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>89730.616</t>
+          <t>-15831802817.6632</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>94077.891</t>
+          <t>-18020874516.0392</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>94257.104</t>
+          <t>-17919786095.2036</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>97040.004</t>
+          <t>-16176269265.3459</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>88964.014</t>
+          <t>-11027794780.9687</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>274121.89465</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>287499.72846</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>268282.01642</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>180435.22768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>227489.32958</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>259521.41133</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>240708.48946</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>270796.19484</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>307219.55963</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>357054.9163</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>416922.20117</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>466492.72549</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>515376.82677</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>459994.19235</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>409732.13588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>28619.112</t>
+          <t>-0.0309977641340441</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27822.144</t>
+          <t>-0.0388482477476826</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27387.823</t>
+          <t>-0.0320610021021113</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25177.847</t>
+          <t>-0.0288575090422438</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25855.563</t>
+          <t>-0.0310096828517504</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>26568.963</t>
+          <t>-0.0189217233926799</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>26135.509</t>
+          <t>-0.0186632671542647</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>26195.6</t>
+          <t>-0.0122468927618182</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>26324.079</t>
+          <t>-0.0126088668947742</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27295.822</t>
+          <t>-0.0040261054710946</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>26174.3</t>
+          <t>-0.00508146704981347</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26083.912</t>
+          <t>-0.00408552312503735</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>25445.415</t>
+          <t>0.00149587664020164</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>25600.676</t>
+          <t>-0.00497395422928803</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>25523.589</t>
+          <t>-0.00601153392119979</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>249110.987205519</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>272393.548705949</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>249618.697610976</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>161334.261309919</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>200645.101910896</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>229288.854944361</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>219964.217061377</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>250739.517668645</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>287975.197009048</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>322535.656092378</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>387647.803112496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>440293.28298971</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>483677.734658298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>439426.781156843</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>390590.697894541</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19870.239</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19356.813</t>
+          <t>429108.845699053</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17753.367</t>
+          <t>393881.896820065</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14788.414</t>
+          <t>257613.676550789</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15128.465</t>
+          <t>312348.682631458</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>16359.771</t>
+          <t>353831.571985482</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16615.458</t>
+          <t>339803.996715696</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17410.753</t>
+          <t>382243.187022735</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18876.923</t>
+          <t>433445.671955757</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20134.114</t>
+          <t>475287.804818375</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20262.716</t>
+          <t>566607.454749689</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>21239.473</t>
+          <t>633380.066717064</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>20641.072</t>
+          <t>684836.2921322</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>19013.475</t>
+          <t>619922.388725574</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17967.595</t>
+          <t>550345.838391702</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>1760829.1189605</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>1877338.60876306</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>1815958.90185428</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>1339132.81334857</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>108.99</t>
+          <t>1562163.15089374</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>100.32</t>
+          <t>1701353.49363953</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>99.45</t>
+          <t>1594994.15101507</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>1798851.73688326</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>83.69</t>
+          <t>2103913.66621226</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>84.05</t>
+          <t>2357180.08736089</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>2795229.38105993</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>73.93</t>
+          <t>3142233.58718998</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>77.57</t>
+          <t>3440728.34002697</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>93.95</t>
+          <t>3360863.6263319</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>3066435.03210023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.835</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.645</t>
+          <t>428589.960716182</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.778</t>
+          <t>441970.169407685</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.273</t>
+          <t>408004.34827534</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.893</t>
+          <t>427374.866036795</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>459218.408752575</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.944</t>
+          <t>485951.913102854</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.707</t>
+          <t>510733.843279555</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.503</t>
+          <t>533263.829689562</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>544828.800386899</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>577464.20665302</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>605129.469906568</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>632759.282473243</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>654996.466782229</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.651</t>
+          <t>660805.520872823</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>249110.987205519</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>271693.846620992</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>277965.695940862</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>251566.758518966</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>274181.471253126</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>297858.188855432</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>314883.476316144</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>336240.636147866</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>357353.197563222</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>372975.201836446</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>397365.382260671</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>424694.737027864</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>448762.49721263</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>464523.411320782</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>468407.377087872</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>91114.8126439805</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>84984.9677209469</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>91659.1544999351</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>70390.3246992115</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>101118.468968542</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>120090.343264518</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>106259.381664304</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>128451.325217265</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>139604.580784243</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>170106.088941625</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>193764.353170311</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>222040.303592935</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>259928.2026578</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>230669.513284426</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>204113.781099333</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>32640760630.5048</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>32366566359.3398</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>32542481626.3838</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>29972519642.6025</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31616610207.0647</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>32772416215.0786</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>33139630374.6316</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>34146108978.1279</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>34675124347.6904</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>37056547061.771</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>36350537931.0334</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>36940810197.7035</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>36652903972.2718</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>36876549870.3788</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>36765508899.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>51162193207.3174</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>50854306766.5198</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>51302683701.8651</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>48438840955.0654</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>50338267495.631</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>51635804554.3794</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>52111252339.1222</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>53200369020.8505</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>53124251939.0588</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>55887330835.7667</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>54220886780.1216</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>54641265800.5858</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>53454995526.7301</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>53781163147.4982</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>53619219783.3406</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>28619111712.7211</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27822143889.0005</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27387822634.399</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>25177846595.1586</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>25855562633.2732</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>26568962791.8559</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>26135509456.5117</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>26195599527.1957</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>26324079477.8952</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>27295821939.2313</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>26174299894.4793</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>26083911950.3647</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>25445415330.4625</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>25600676227.8962</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>25523588649.4501</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20398000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20837000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21201000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>19918000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20277000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21136000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21557000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22152000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22117000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>22534000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22830000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>23133000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>23418000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>23560890.1689708</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>23489944.7004608</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12899000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13200000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13405000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12296000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>12663000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13361000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13659000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14182000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14403000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14894000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>15186000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15551000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15970000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>16067444.5297832</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16019062.9800307</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>51162193207.3174</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>50854306766.5198</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>51302683701.8651</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48438840955.0654</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>50338267495.631</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>51635804554.3794</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>52111252339.1222</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>53200369020.8505</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>53124251939.0588</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>55887330835.7667</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>54220886780.1216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>54641265800.5858</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>53454995526.7301</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>53781163147.4982</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>53619219783.3406</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32640760630.5048</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>32366566359.3398</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>32542481626.3838</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>29972519642.6025</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>31616610207.0647</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>32772416215.0786</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>33139630374.6316</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>34146108978.1279</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>34675124347.6904</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>37056547061.771</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>36350537931.0334</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>36940810197.7035</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>36652903972.2718</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>36876549870.3788</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>36765508899.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.331716691795572</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.354037887688592</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.360021341046824</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.385882898215127</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.39689266710716</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.399947745631216</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.427682288313345</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.457678077948967</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.463015386857404</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.469383418714181</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.436166942521148</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.430448852721004</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.435615610218396</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.42882899269932</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.419954649183771</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.427606828039</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.418059720586339</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.403877621841788</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.403828393058087</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.410036099509903</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.203544937111852</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.186941831018976</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.175791620163351</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.156716680514124</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.15458125513764</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.143873997758355</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.125686562528887</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.109872871637817</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.10458479151308</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0920090532044868</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.264457196852025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.279162503358605</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.289349291432411</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.313902096132527</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.325542157096532</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.32708265847282</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.342450577055497</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.372650802730414</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.379068724074233</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.385820132625152</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.468885762181886</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.46768117868951</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.470119431690414</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.465859789604328</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.459922710933326</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.467590107354008</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.467462732560993</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.456048864718562</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.455280579791477</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.462053049660315</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.23808561239466</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.224584889380456</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.211959848305746</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.191666685691717</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.185963703398713</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.176755805601743</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.161515261812081</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.142728903979596</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.137079267562861</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.123555389143104</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1108509.34671</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1192915.35281</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1131548.8462</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>789859.03294</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>995264.19459</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1154386.08155</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1074724.66787</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1220729.34865</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1373053.82031</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1590214.92382</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1913875.12857</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2184540.4385</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2450518.8305</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2409391.66177</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2086877.38964</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>481503.17054</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>514093.81342</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>485541.05132</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>328004.00125</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>413467.1516</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>473921.91525</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>446063.37838</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>510694.51224</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>573050.25274</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>645393.89376</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>760371.80792</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>855420.37031</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>944764.49479</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>850591.90201</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>754935.69005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1354483967.86827</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1457969032.78694</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1552067726.24768</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1607502307.4535</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1670427170.49331</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1744651239.55253</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1816305945.149</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1895039613.93994</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1977196331.69843</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2058958231.97673</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2140992828.15616</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2225192944.02245</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2313261489.50933</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2392646349.28768</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2465814200.56571</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
